--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepoinfo001cc.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepoinfo001cc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7860"/>
+    <workbookView windowWidth="18405" windowHeight="6450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
     <t>已完成额度（万元）</t>
   </si>
   <si>
-    <t>交易完成度</t>
+    <t>交易完成度%</t>
   </si>
   <si>
     <t>备注</t>
@@ -74,9 +74,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -87,21 +87,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -110,16 +155,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -127,58 +181,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -192,33 +194,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -233,13 +233,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,169 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,30 +424,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,17 +442,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,26 +458,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -533,6 +485,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -541,10 +541,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -553,133 +553,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1052,6 +1052,7 @@
     <col min="9" max="9" width="11.45" customWidth="1"/>
     <col min="10" max="10" width="11.3666666666667" customWidth="1"/>
     <col min="11" max="11" width="17.0916666666667" customWidth="1"/>
+    <col min="16" max="16" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepoinfo001cc.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepoinfo001cc.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\pushCode\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE5F59A-B4B3-4322-B410-708B2AB40E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18408" windowHeight="6456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>指令编号</t>
   </si>
@@ -66,13 +72,17 @@
   </si>
   <si>
     <t>指令状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -133,72 +143,6 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
     <mruColors>
       <color rgb="FF000000"/>
     </mruColors>
@@ -206,6 +150,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -219,7 +166,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCEDC7"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -497,8 +444,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
@@ -513,7 +460,7 @@
     <col min="16" max="16" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,6 +511,9 @@
       </c>
       <c r="Q1" t="s">
         <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -573,7 +523,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
